--- a/docs/unit2/09_seismic/files/seismic_foundation_KEY.xlsx
+++ b/docs/unit2/09_seismic/files/seismic_foundation_KEY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/temp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6822D13A-840F-7048-9840-27CFA8B5FC18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443835CB-CB81-724F-96FD-1C6AFDF8B362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5560" yWindow="4280" windowWidth="34200" windowHeight="20240" activeTab="2" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="5560" yWindow="4280" windowWidth="34200" windowHeight="20240" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -1074,10 +1074,10 @@
     <xf numFmtId="0" fontId="16" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7959,11 +7959,11 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
       <c r="F7" s="15" t="s">
         <v>15</v>
       </c>
@@ -9341,36 +9341,36 @@
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
+      <c r="J7" s="43"/>
       <c r="K7" s="1"/>
-      <c r="L7" s="44" t="s">
+      <c r="L7" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="M7" s="44"/>
-      <c r="N7" s="44"/>
-      <c r="O7" s="44"/>
-      <c r="P7" s="44"/>
-      <c r="Q7" s="44"/>
-      <c r="R7" s="44" t="s">
+      <c r="M7" s="43"/>
+      <c r="N7" s="43"/>
+      <c r="O7" s="43"/>
+      <c r="P7" s="43"/>
+      <c r="Q7" s="43"/>
+      <c r="R7" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="S7" s="44"/>
-      <c r="T7" s="44"/>
-      <c r="U7" s="44"/>
-      <c r="V7" s="44"/>
-      <c r="W7" s="44" t="s">
+      <c r="S7" s="43"/>
+      <c r="T7" s="43"/>
+      <c r="U7" s="43"/>
+      <c r="V7" s="43"/>
+      <c r="W7" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="X7" s="44"/>
+      <c r="X7" s="43"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="20" t="s">
@@ -9460,7 +9460,8 @@
         <v>67</v>
       </c>
       <c r="E9" s="3">
-        <v>600</v>
+        <f>800*0.8</f>
+        <v>640</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
